--- a/out/Attention-Mamba1_repeat_5_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_5_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_5_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.009526357054710388</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.72</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01061636209487915</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7899999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.009821906685829163</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.009972736239433289</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.008695147931575775</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.008943766355514526</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.009852252900600433</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.00854811817407608</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.007965005934238434</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.007885664701461792</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.008023150265216827</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.007750794291496277</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.007478982210159302</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.00771910697221756</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.007716342806816101</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01005548983812332</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.009861469268798828</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01562369242310524</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01103966683149338</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01607324555516243</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01324543356895447</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.009849436581134796</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.008120134472846985</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.009518332779407501</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.00806475430727005</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.008312143385410309</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.009422384202480316</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.008062869310379028</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.008437998592853546</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.008883237838745117</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01788100600242615</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01136144995689392</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01091226935386658</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.009542845189571381</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.008201964199542999</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.009353786706924438</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0086837038397789</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.008301801979541779</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.008517146110534668</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.008886329829692841</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.008823610842227936</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.007987014949321747</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.007594376802444458</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.008269719779491425</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.007993347942829132</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.007931850850582123</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.008389689028263092</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.007823556661605835</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.008136220276355743</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.007864624261856079</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.008579179644584656</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.008186794817447662</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.007964111864566803</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.008933268487453461</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.008118085563182831</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01063355058431625</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.00898405909538269</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.009345076978206635</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.009165890514850616</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.008394293487071991</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.008937403559684753</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.007660657167434692</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.007626652717590332</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.00740891695022583</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.007090054452419281</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.007942967116832733</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.007620617747306824</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.007458940148353577</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.007987700402736664</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.007758654654026031</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.006533339619636536</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.007203437387943268</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01794858276844025</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01297775283455849</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.02328876778483391</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01594498008489609</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.0151032917201519</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01070459187030792</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01025813817977905</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01024355739355087</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01081401854753494</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01346509158611298</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.009910084307193756</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01180224120616913</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.009990215301513672</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.009075872600078583</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.01641752198338509</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0129777118563652</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01132360100746155</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.009410679340362549</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01021638512611389</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.009343825280666351</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.009327992796897888</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.0103180855512619</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01206255704164505</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01033226400613785</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01006589084863663</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.0100734680891037</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.008924856781959534</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.009783647954463959</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01225278526544571</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01051778346300125</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.01032682508230209</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.01167108863592148</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01211597770452499</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.009649217128753662</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.01121299713850021</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.009163253009319305</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.009458191692829132</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.007174268364906311</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.007014170289039612</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.007214635610580444</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0270046666264534</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.01053196936845779</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.03863135725259781</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01820637658238411</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.02924488484859467</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01426076889038086</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.008832260966300964</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.007810406386852264</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.02535421773791313</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.02167505025863647</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.04486612603068352</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.01008694618940353</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.6500000000000004</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.007292762398719788</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_5_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000005.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.009526357054710388</v>
+        <v>0.009526349604129791</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.72</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.01061636209487915</v>
+        <v>0.01061639934778214</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.7899999999999999</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.009821906685829163</v>
+        <v>0.009821899235248566</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.8599999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.009972736239433289</v>
+        <v>0.009972728788852692</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.8599999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.008695147931575775</v>
+        <v>0.008695110678672791</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.008943766355514526</v>
+        <v>0.008943744003772736</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.009852252900600433</v>
+        <v>0.009852267801761627</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.00854811817407608</v>
+        <v>0.008548125624656677</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.007965005934238434</v>
+        <v>0.007965020835399628</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.007885664701461792</v>
+        <v>0.007885672152042389</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.008023150265216827</v>
+        <v>0.008023157715797424</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.007750794291496277</v>
+        <v>0.007750801742076874</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.007478982210159302</v>
+        <v>0.007478997111320496</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.00771910697221756</v>
+        <v>0.007719099521636963</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.1199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.007716342806816101</v>
+        <v>0.007716350257396698</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.01005548983812332</v>
+        <v>0.01005547493696213</v>
       </c>
       <c r="JB17" t="n">
         <v>0.4399999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.01562369242310524</v>
+        <v>0.01562368497252464</v>
       </c>
       <c r="JB19" t="n">
         <v>0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.01103966683149338</v>
+        <v>0.01103963702917099</v>
       </c>
       <c r="JB20" t="n">
         <v>0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.009849436581134796</v>
+        <v>0.009849429130554199</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.008120134472846985</v>
+        <v>0.008120141923427582</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.00806475430727005</v>
+        <v>0.008064776659011841</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.008312143385410309</v>
+        <v>0.008312135934829712</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.009422384202480316</v>
+        <v>0.009422376751899719</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.8599999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.008062869310379028</v>
+        <v>0.008062861859798431</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.8599999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.01788100600242615</v>
+        <v>0.01788101345300674</v>
       </c>
       <c r="JB32" t="n">
         <v>0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.01136144995689392</v>
+        <v>0.01136142760515213</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.01091226935386658</v>
+        <v>0.01091229170560837</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.009542845189571381</v>
+        <v>0.009542852640151978</v>
       </c>
       <c r="JB35" t="n">
         <v>0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.008201964199542999</v>
+        <v>0.008201949298381805</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.1199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.009353786706924438</v>
+        <v>0.009353823959827423</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.0086837038397789</v>
+        <v>0.008683726191520691</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.008301801979541779</v>
+        <v>0.008301794528961182</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.008517146110534668</v>
+        <v>0.008517123758792877</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.008886329829692841</v>
+        <v>0.008886344730854034</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.008823610842227936</v>
+        <v>0.008823603391647339</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.007594376802444458</v>
+        <v>0.007594361901283264</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.008269719779491425</v>
+        <v>0.008269704878330231</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.007993347942829132</v>
+        <v>0.007993362843990326</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.007931850850582123</v>
+        <v>0.007931865751743317</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.007823556661605835</v>
+        <v>0.007823571562767029</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.007864624261856079</v>
+        <v>0.00786464661359787</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.008579179644584656</v>
+        <v>0.008579187095165253</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.007964111864566803</v>
+        <v>0.007964104413986206</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.2599999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.008118085563182831</v>
+        <v>0.008118093013763428</v>
       </c>
       <c r="JB56" t="n">
         <v>0.16</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.01063355058431625</v>
+        <v>0.01063356548547745</v>
       </c>
       <c r="JB57" t="n">
         <v>0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.00898405909538269</v>
+        <v>0.008984051644802094</v>
       </c>
       <c r="JB58" t="n">
         <v>0.4399999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.009345076978206635</v>
+        <v>0.009345099329948425</v>
       </c>
       <c r="JB59" t="n">
         <v>0.4399999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.008394293487071991</v>
+        <v>0.008394278585910797</v>
       </c>
       <c r="JB61" t="n">
         <v>0.16</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.008937403559684753</v>
+        <v>0.008937425911426544</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.007660657167434692</v>
+        <v>0.007660642266273499</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.8599999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.00740891695022583</v>
+        <v>0.007408909499645233</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.007090054452419281</v>
+        <v>0.007090069353580475</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.007942967116832733</v>
+        <v>0.007942982017993927</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.007620617747306824</v>
+        <v>0.007620625197887421</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.8599999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.007458940148353577</v>
+        <v>0.00745893269777298</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.8599999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.007987700402736664</v>
+        <v>0.007987707853317261</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.8599999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.007758654654026031</v>
+        <v>0.007758624851703644</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.2599999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.006533339619636536</v>
+        <v>0.006533332169055939</v>
       </c>
       <c r="JB72" t="n">
         <v>0.02000000000000007</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.007203437387943268</v>
+        <v>0.007203429937362671</v>
       </c>
       <c r="JB73" t="n">
         <v>0.16</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.01794858276844025</v>
+        <v>0.01794859394431114</v>
       </c>
       <c r="JB74" t="n">
         <v>0.4399999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.01297775283455849</v>
+        <v>0.01297777518630028</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.02328876778483391</v>
+        <v>0.0232887826859951</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.01594498008489609</v>
+        <v>0.01594499871134758</v>
       </c>
       <c r="JB77" t="n">
         <v>0.8599999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.0151032917201519</v>
+        <v>0.0151032954454422</v>
       </c>
       <c r="JB78" t="n">
         <v>0.7199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.01070459187030792</v>
+        <v>0.01070459932088852</v>
       </c>
       <c r="JB79" t="n">
         <v>0.5799999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.01025813817977905</v>
+        <v>0.01025813072919846</v>
       </c>
       <c r="JB80" t="n">
         <v>0.4399999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.01024355739355087</v>
+        <v>0.01024354994297028</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.3</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.01346509158611298</v>
+        <v>0.01346510648727417</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.16</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.009910084307193756</v>
+        <v>0.009910069406032562</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.3</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.01180224120616913</v>
+        <v>0.01180225610733032</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.4399999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.009990215301513672</v>
+        <v>0.009990230202674866</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.009075872600078583</v>
+        <v>0.009075865149497986</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.1600000000000001</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.0129777118563652</v>
+        <v>0.0129777193069458</v>
       </c>
       <c r="JB89" t="n">
         <v>0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.01132360100746155</v>
+        <v>0.01132361590862274</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.009410679340362549</v>
+        <v>0.009410656988620758</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.5799999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.01021638512611389</v>
+        <v>0.01021639257669449</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.8599999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.009343825280666351</v>
+        <v>0.009343788027763367</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.009327992796897888</v>
+        <v>0.009327977895736694</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.0103180855512619</v>
+        <v>0.0103180930018425</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.01206255704164505</v>
+        <v>0.01206253468990326</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.01006589084863663</v>
+        <v>0.01006591320037842</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.0100734680891037</v>
+        <v>0.01007343828678131</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.008924856781959534</v>
+        <v>0.008924864232540131</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.009783647954463959</v>
+        <v>0.009783655405044556</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.01225278526544571</v>
+        <v>0.0122528076171875</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.1199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.01051778346300125</v>
+        <v>0.01051781326532364</v>
       </c>
       <c r="JB103" t="n">
         <v>0.02000000000000007</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.01032682508230209</v>
+        <v>0.01032685488462448</v>
       </c>
       <c r="JB104" t="n">
         <v>0.3</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.01211597770452499</v>
+        <v>0.01211600005626678</v>
       </c>
       <c r="JB106" t="n">
         <v>0.3</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.009649217128753662</v>
+        <v>0.009649209678173065</v>
       </c>
       <c r="JB107" t="n">
         <v>0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.01121299713850021</v>
+        <v>0.01121300458908081</v>
       </c>
       <c r="JB108" t="n">
         <v>0.1600000000000001</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.009163253009319305</v>
+        <v>0.009163245558738708</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.1199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.009458191692829132</v>
+        <v>0.009458176791667938</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.007174268364906311</v>
+        <v>0.007174275815486908</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.007014170289039612</v>
+        <v>0.007014200091362</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.007214635610580444</v>
+        <v>0.007214643061161041</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.0270046666264534</v>
+        <v>0.02700464800000191</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.4399999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.03863135725259781</v>
+        <v>0.0386313758790493</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.01820637658238411</v>
+        <v>0.01820641383528709</v>
       </c>
       <c r="JB117" t="n">
         <v>0.5799999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.02924488484859467</v>
+        <v>0.02924488857388496</v>
       </c>
       <c r="JB118" t="n">
         <v>0.5799999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.01426076889038086</v>
+        <v>0.01426076516509056</v>
       </c>
       <c r="JB119" t="n">
         <v>0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.008832260966300964</v>
+        <v>0.008832268416881561</v>
       </c>
       <c r="JB120" t="n">
         <v>0.3</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.007810406386852264</v>
+        <v>0.007810398936271667</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.02535421773791313</v>
+        <v>0.02535422146320343</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.02167505025863647</v>
+        <v>0.02167508006095886</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.04486612603068352</v>
+        <v>0.04486614465713501</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.01008694618940353</v>
+        <v>0.01008693873882294</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.6500000000000004</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.007292762398719788</v>
+        <v>0.007292777299880981</v>
       </c>
       <c r="JB126" t="n">
         <v>-1</v>
